--- a/web/public/forms/orig/o-jangbi-gwanri.xlsx
+++ b/web/public/forms/orig/o-jangbi-gwanri.xlsx
@@ -822,7 +822,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="57" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="57" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="57" t="inlineStr">
@@ -3789,7 +3789,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="57" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="57" t="inlineStr">
@@ -5773,7 +5773,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -9271,7 +9271,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -9843,7 +9843,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -10398,7 +10398,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -12319,7 +12319,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="57" t="inlineStr">
@@ -13969,7 +13969,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="I1" s="57" t="inlineStr">

--- a/web/public/forms/orig/o-jangbi-gwanri.xlsx
+++ b/web/public/forms/orig/o-jangbi-gwanri.xlsx
@@ -797,7 +797,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
